--- a/testdata/Move (1).xlsx
+++ b/testdata/Move (1).xlsx
@@ -321,7 +321,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="12.63" customWidth="1" style="2" min="1" max="6"/>
@@ -364,18 +364,29 @@
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" s="2">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>1111</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>3333</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1" s="2"/>
+    <row r="6" ht="15.75" customHeight="1" s="2">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4333</t>
+        </is>
+      </c>
+    </row>
     <row r="7" ht="15.75" customHeight="1" s="2"/>
     <row r="8" ht="15.75" customHeight="1" s="2"/>
     <row r="9" ht="15.75" customHeight="1" s="2"/>
